--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484109_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484109_PROCESSED_CHRONO.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>M. AGUILO RODRIGUEZ</t>
+          <t>P. CAMÍ GALERA</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.5396</v>
+        <v>5.9349</v>
       </c>
       <c r="E2" t="n">
-        <v>6.0202</v>
+        <v>6.7372</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5194</v>
+        <v>-0.8023</v>
       </c>
       <c r="G2" t="n">
-        <v>4.4437</v>
+        <v>4.8523</v>
       </c>
       <c r="H2" t="n">
-        <v>4.3193</v>
+        <v>4.158</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1244</v>
+        <v>0.6944</v>
       </c>
       <c r="J2" t="n">
-        <v>4.2637</v>
+        <v>7.236</v>
       </c>
       <c r="K2" t="n">
-        <v>4.7029</v>
+        <v>4.8186</v>
       </c>
       <c r="L2" t="n">
-        <v>-0.4392</v>
+        <v>2.4174</v>
       </c>
       <c r="M2" t="n">
-        <v>0.18</v>
+        <v>-2.3837</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.3837</v>
+        <v>-0.6607</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5637</v>
+        <v>-1.723</v>
       </c>
       <c r="P2" t="n">
-        <v>0.7935</v>
+        <v>1.3887</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R2" t="n">
-        <v>2.7774</v>
+        <v>2.3806</v>
       </c>
       <c r="S2" t="n">
-        <v>2.4413</v>
+        <v>-0.3061</v>
       </c>
       <c r="T2" t="n">
-        <v>3.2083</v>
+        <v>0.4932</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.767</v>
+        <v>-0.7993</v>
       </c>
       <c r="V2" t="n">
-        <v>-1.139</v>
+        <v>0</v>
       </c>
       <c r="W2" t="n">
-        <v>0.532</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>-1.671</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. CAMÍ GALERA</t>
+          <t>M. AGUILO RODRIGUEZ</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.3533</v>
+        <v>5.0179</v>
       </c>
       <c r="E3" t="n">
-        <v>5.819</v>
+        <v>4.246</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.4657</v>
+        <v>0.7719</v>
       </c>
       <c r="G3" t="n">
-        <v>4.8523</v>
+        <v>4.4437</v>
       </c>
       <c r="H3" t="n">
-        <v>4.158</v>
+        <v>4.3193</v>
       </c>
       <c r="I3" t="n">
-        <v>0.6944</v>
+        <v>0.1244</v>
       </c>
       <c r="J3" t="n">
-        <v>7.236</v>
+        <v>4.2637</v>
       </c>
       <c r="K3" t="n">
-        <v>4.8186</v>
+        <v>4.7029</v>
       </c>
       <c r="L3" t="n">
-        <v>2.4174</v>
+        <v>-0.4392</v>
       </c>
       <c r="M3" t="n">
-        <v>-2.3837</v>
+        <v>0.18</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.6607</v>
+        <v>-0.3837</v>
       </c>
       <c r="O3" t="n">
-        <v>-1.723</v>
+        <v>0.5637</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3887</v>
+        <v>0.7935</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R3" t="n">
-        <v>2.3806</v>
+        <v>2.7774</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.8877</v>
+        <v>0.9197</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.4251</v>
+        <v>1.4342</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4626</v>
+        <v>-0.5145</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>-1.139</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>0.532</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>-1.671</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>X. ANDREU GARI</t>
+          <t>P. FLUXA PAYERAS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,64 +721,64 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.0019</v>
+        <v>3.0295</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.2194</v>
+        <v>0.8751</v>
       </c>
       <c r="F4" t="n">
-        <v>3.2213</v>
+        <v>2.1544</v>
       </c>
       <c r="G4" t="n">
-        <v>1.3734</v>
+        <v>-0.4806</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.9675</v>
+        <v>0.8512999999999999</v>
       </c>
       <c r="I4" t="n">
-        <v>2.341</v>
+        <v>-1.3318</v>
       </c>
       <c r="J4" t="n">
-        <v>0.523</v>
+        <v>-0.9933</v>
       </c>
       <c r="K4" t="n">
-        <v>-1.2543</v>
+        <v>0.7661</v>
       </c>
       <c r="L4" t="n">
-        <v>1.7773</v>
+        <v>-1.7595</v>
       </c>
       <c r="M4" t="n">
-        <v>0.8504</v>
+        <v>0.5127</v>
       </c>
       <c r="N4" t="n">
-        <v>0.2867</v>
+        <v>0.0851</v>
       </c>
       <c r="O4" t="n">
-        <v>0.5637</v>
+        <v>0.4276</v>
       </c>
       <c r="P4" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R4" t="n">
-        <v>2.3806</v>
+        <v>1.3887</v>
       </c>
       <c r="S4" t="n">
-        <v>1.1642</v>
+        <v>0.367</v>
       </c>
       <c r="T4" t="n">
-        <v>1.2414</v>
+        <v>0.1815</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.0772</v>
+        <v>0.1855</v>
       </c>
       <c r="V4" t="n">
-        <v>0.0675</v>
+        <v>2.7464</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>2.6789</v>
       </c>
       <c r="X4" t="n">
         <v>0.0675</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>P. FLUXA PAYERAS</t>
+          <t>X. ANDREU GARI</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,64 +799,64 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.077</v>
+        <v>2.2939</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1055</v>
+        <v>-0.8712</v>
       </c>
       <c r="F5" t="n">
-        <v>2.1825</v>
+        <v>3.1651</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.4806</v>
+        <v>1.3734</v>
       </c>
       <c r="H5" t="n">
-        <v>0.8512999999999999</v>
+        <v>-0.9675</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.3318</v>
+        <v>2.341</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.9933</v>
+        <v>0.523</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7661</v>
+        <v>-1.2543</v>
       </c>
       <c r="L5" t="n">
-        <v>-1.7595</v>
+        <v>1.7773</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5127</v>
+        <v>0.8504</v>
       </c>
       <c r="N5" t="n">
-        <v>0.0851</v>
+        <v>0.2867</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4276</v>
+        <v>0.5637</v>
       </c>
       <c r="P5" t="n">
         <v>0.3968</v>
       </c>
       <c r="Q5" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3887</v>
+        <v>2.3806</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.5856</v>
+        <v>0.4563</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.7991</v>
+        <v>0.5896</v>
       </c>
       <c r="U5" t="n">
-        <v>0.2136</v>
+        <v>-0.1333</v>
       </c>
       <c r="V5" t="n">
-        <v>2.7464</v>
+        <v>0.0675</v>
       </c>
       <c r="W5" t="n">
-        <v>2.6789</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
         <v>0.0675</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.6102</v>
+        <v>2.0285</v>
       </c>
       <c r="E6" t="n">
-        <v>3.3531</v>
+        <v>3.6592</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.7429</v>
+        <v>-1.6307</v>
       </c>
       <c r="G6" t="n">
         <v>1.3208</v>
@@ -922,13 +922,13 @@
         <v>0.5952</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.5203</v>
+        <v>-0.102</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3117</v>
+        <v>-0.0056</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2086</v>
+        <v>-0.0964</v>
       </c>
       <c r="V6" t="n">
         <v>1.2065</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>C. POYATOS PARRA</t>
+          <t>L. SANCHEZ MORENO</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.6074</v>
+        <v>1.1287</v>
       </c>
       <c r="E7" t="n">
-        <v>4.2858</v>
+        <v>3.5024</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.6784</v>
+        <v>-2.3737</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.2392</v>
+        <v>-1.2279</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.1588</v>
+        <v>-1.6838</v>
       </c>
       <c r="I7" t="n">
-        <v>-1.0804</v>
+        <v>0.4559</v>
       </c>
       <c r="J7" t="n">
-        <v>1.7493</v>
+        <v>2.6246</v>
       </c>
       <c r="K7" t="n">
-        <v>0.3035</v>
+        <v>-0.3576</v>
       </c>
       <c r="L7" t="n">
-        <v>1.4458</v>
+        <v>2.9822</v>
       </c>
       <c r="M7" t="n">
-        <v>-3.9885</v>
+        <v>-3.8524</v>
       </c>
       <c r="N7" t="n">
-        <v>-1.4622</v>
+        <v>-1.3262</v>
       </c>
       <c r="O7" t="n">
         <v>-2.5262</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9919</v>
+        <v>2.1822</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.9838</v>
+        <v>-0.9919</v>
       </c>
       <c r="R7" t="n">
-        <v>2.9758</v>
+        <v>3.1741</v>
       </c>
       <c r="S7" t="n">
-        <v>0.8502999999999999</v>
+        <v>-0.1629</v>
       </c>
       <c r="T7" t="n">
-        <v>1.984</v>
+        <v>0.6633</v>
       </c>
       <c r="U7" t="n">
-        <v>-1.1337</v>
+        <v>-0.8262</v>
       </c>
       <c r="V7" t="n">
-        <v>2.0044</v>
+        <v>0.3373</v>
       </c>
       <c r="W7" t="n">
-        <v>2.5364</v>
+        <v>1.2065</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.532</v>
+        <v>-0.8692</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.967</v>
+        <v>0.8228</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3891</v>
+        <v>-0.2248</v>
       </c>
       <c r="F8" t="n">
-        <v>1.3561</v>
+        <v>1.0475</v>
       </c>
       <c r="G8" t="n">
         <v>2.1834</v>
@@ -1078,13 +1078,13 @@
         <v>0.7935</v>
       </c>
       <c r="S8" t="n">
-        <v>0.9902</v>
+        <v>0.8459</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.0679</v>
+        <v>0.0964</v>
       </c>
       <c r="U8" t="n">
-        <v>1.0581</v>
+        <v>0.7495000000000001</v>
       </c>
       <c r="V8" t="n">
         <v>-2.0082</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>L. SANCHEZ MORENO</t>
+          <t>C. POYATOS PARRA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2946</v>
+        <v>0.7912</v>
       </c>
       <c r="E9" t="n">
-        <v>2.5841</v>
+        <v>3.4695</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2895</v>
+        <v>-2.6784</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.2279</v>
+        <v>-2.2392</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.6838</v>
+        <v>-1.1588</v>
       </c>
       <c r="I9" t="n">
-        <v>0.4559</v>
+        <v>-1.0804</v>
       </c>
       <c r="J9" t="n">
-        <v>2.6246</v>
+        <v>1.7493</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.3576</v>
+        <v>0.3035</v>
       </c>
       <c r="L9" t="n">
-        <v>2.9822</v>
+        <v>1.4458</v>
       </c>
       <c r="M9" t="n">
-        <v>-3.8524</v>
+        <v>-3.9885</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.3262</v>
+        <v>-1.4622</v>
       </c>
       <c r="O9" t="n">
         <v>-2.5262</v>
       </c>
       <c r="P9" t="n">
-        <v>2.1822</v>
+        <v>0.9919</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9919</v>
+        <v>-1.9838</v>
       </c>
       <c r="R9" t="n">
-        <v>3.1741</v>
+        <v>2.9758</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.997</v>
+        <v>0.034</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.255</v>
+        <v>1.1678</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.7421</v>
+        <v>-1.1337</v>
       </c>
       <c r="V9" t="n">
-        <v>0.3373</v>
+        <v>2.0044</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2065</v>
+        <v>2.5364</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.8692</v>
+        <v>-0.532</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.1411</v>
+        <v>-0.1579</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.31</v>
+        <v>-0.6355</v>
       </c>
       <c r="F10" t="n">
-        <v>0.1689</v>
+        <v>0.4775</v>
       </c>
       <c r="G10" t="n">
         <v>-0.5046</v>
@@ -1234,13 +1234,13 @@
         <v>1.3887</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.7635</v>
+        <v>0.2196</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.5044</v>
+        <v>0.1702</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2591</v>
+        <v>0.0495</v>
       </c>
       <c r="V10" t="n">
         <v>-0.2698</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-6.6848</v>
+        <v>-6.9526</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.4149</v>
+        <v>-3.823</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2699</v>
+        <v>-3.1296</v>
       </c>
       <c r="G11" t="n">
         <v>-5.0496</v>
@@ -1312,13 +1312,13 @@
         <v>0.9919</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3486</v>
+        <v>0.0808</v>
       </c>
       <c r="T11" t="n">
-        <v>0.7483</v>
+        <v>0.3402</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.3996</v>
+        <v>-0.2594</v>
       </c>
       <c r="V11" t="n">
         <v>0</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>13.6251</v>
+        <v>13.9369</v>
       </c>
       <c r="E12" t="n">
-        <v>16.6233</v>
+        <v>16.9349</v>
       </c>
       <c r="F12" t="n">
-        <v>-2.998199999999999</v>
+        <v>-2.9983</v>
       </c>
       <c r="G12" t="n">
         <v>4.6717</v>
@@ -1363,7 +1363,7 @@
         <v>4.0162</v>
       </c>
       <c r="J12" t="n">
-        <v>17.05070000000001</v>
+        <v>17.0507</v>
       </c>
       <c r="K12" t="n">
         <v>5.8774</v>
@@ -1375,7 +1375,7 @@
         <v>-12.3789</v>
       </c>
       <c r="N12" t="n">
-        <v>-5.2218</v>
+        <v>-5.221800000000001</v>
       </c>
       <c r="O12" t="n">
         <v>-7.157</v>
@@ -1390,16 +1390,16 @@
         <v>18.8465</v>
       </c>
       <c r="S12" t="n">
-        <v>2.0405</v>
+        <v>2.3523</v>
       </c>
       <c r="T12" t="n">
-        <v>4.8188</v>
+        <v>5.130800000000001</v>
       </c>
       <c r="U12" t="n">
-        <v>-2.7782</v>
+        <v>-2.7783</v>
       </c>
       <c r="V12" t="n">
-        <v>2.945099999999999</v>
+        <v>2.9451</v>
       </c>
       <c r="W12" t="n">
         <v>9.6328</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>4.177</v>
+        <v>3.4704</v>
       </c>
       <c r="E13" t="n">
-        <v>2.4527</v>
+        <v>1.9426</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7243</v>
+        <v>1.5279</v>
       </c>
       <c r="G13" t="n">
         <v>1.1645</v>
@@ -1468,13 +1468,13 @@
         <v>1.9838</v>
       </c>
       <c r="S13" t="n">
-        <v>0.9347</v>
+        <v>0.2282</v>
       </c>
       <c r="T13" t="n">
-        <v>0.9807</v>
+        <v>0.4706</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.046</v>
+        <v>-0.2424</v>
       </c>
       <c r="V13" t="n">
         <v>1.0858</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.8967</v>
+        <v>2.9205</v>
       </c>
       <c r="E14" t="n">
         <v>3.1609</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.2642</v>
+        <v>-0.2404</v>
       </c>
       <c r="G14" t="n">
         <v>0.9283</v>
@@ -1546,13 +1546,13 @@
         <v>1.1903</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2562</v>
+        <v>-0.2324</v>
       </c>
       <c r="T14" t="n">
         <v>0.2438</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.5</v>
+        <v>-0.4762</v>
       </c>
       <c r="V14" t="n">
         <v>2.0263</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.3913</v>
+        <v>2.0546</v>
       </c>
       <c r="E15" t="n">
         <v>3.6683</v>
       </c>
       <c r="F15" t="n">
-        <v>-1.277</v>
+        <v>-1.6136</v>
       </c>
       <c r="G15" t="n">
         <v>0.928</v>
@@ -1624,13 +1624,13 @@
         <v>1.5871</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3877</v>
+        <v>0.051</v>
       </c>
       <c r="T15" t="n">
         <v>0.0057</v>
       </c>
       <c r="U15" t="n">
-        <v>0.3819</v>
+        <v>0.0452</v>
       </c>
       <c r="V15" t="n">
         <v>1.4724</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7352</v>
+        <v>0.8449</v>
       </c>
       <c r="E16" t="n">
-        <v>3.3664</v>
+        <v>3.6725</v>
       </c>
       <c r="F16" t="n">
-        <v>-2.6312</v>
+        <v>-2.8276</v>
       </c>
       <c r="G16" t="n">
         <v>5.2905</v>
@@ -1702,13 +1702,13 @@
         <v>1.7855</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1253</v>
+        <v>-0.0156</v>
       </c>
       <c r="T16" t="n">
-        <v>0.1928</v>
+        <v>0.4989</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.3181</v>
+        <v>-0.5145</v>
       </c>
       <c r="V16" t="n">
         <v>-1.2558</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.2731</v>
+        <v>-0.9661999999999999</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.6496</v>
+        <v>-0.9557</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.6235000000000001</v>
+        <v>-0.0106</v>
       </c>
       <c r="G17" t="n">
         <v>1.7012</v>
@@ -1780,13 +1780,13 @@
         <v>2.3806</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.8779</v>
+        <v>-0.5711000000000001</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9184</v>
+        <v>0.6123</v>
       </c>
       <c r="U17" t="n">
-        <v>-1.7963</v>
+        <v>-1.1833</v>
       </c>
       <c r="V17" t="n">
         <v>0.4826</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.4686</v>
+        <v>-2.2389</v>
       </c>
       <c r="E18" t="n">
-        <v>3.4388</v>
+        <v>2.7246</v>
       </c>
       <c r="F18" t="n">
-        <v>-4.9073</v>
+        <v>-4.9634</v>
       </c>
       <c r="G18" t="n">
         <v>-0.277</v>
@@ -1858,13 +1858,13 @@
         <v>0.7935</v>
       </c>
       <c r="S18" t="n">
-        <v>0.6938</v>
+        <v>-0.0765</v>
       </c>
       <c r="T18" t="n">
-        <v>1.06</v>
+        <v>0.3458</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3662</v>
+        <v>-0.4223</v>
       </c>
       <c r="V18" t="n">
         <v>-2.6789</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-2.5603</v>
+        <v>-2.256</v>
       </c>
       <c r="E19" t="n">
         <v>-1.3152</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.2452</v>
+        <v>-0.9408</v>
       </c>
       <c r="G19" t="n">
         <v>-2.3495</v>
@@ -1936,13 +1936,13 @@
         <v>0.9919</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.2109</v>
+        <v>0.0935</v>
       </c>
       <c r="T19" t="n">
         <v>0.3175</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.5283</v>
+        <v>-0.224</v>
       </c>
       <c r="V19" t="n">
         <v>0</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-3.9242</v>
+        <v>-4.1121</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.795</v>
+        <v>-2.2031</v>
       </c>
       <c r="F20" t="n">
-        <v>-2.1292</v>
+        <v>-1.909</v>
       </c>
       <c r="G20" t="n">
         <v>-3.7005</v>
@@ -2014,13 +2014,13 @@
         <v>1.5871</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0278</v>
+        <v>-0.1601</v>
       </c>
       <c r="T20" t="n">
-        <v>0.9184</v>
+        <v>0.5103</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.8905999999999999</v>
+        <v>-0.6704</v>
       </c>
       <c r="V20" t="n">
         <v>0.1453</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>V. VINÓS ALTEMIR</t>
+          <t>M. DUCH CABEZAS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.4562</v>
+        <v>-4.1764</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.873</v>
+        <v>-2.0281</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.5832</v>
+        <v>-2.1483</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.4988</v>
+        <v>-2.5694</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4792</v>
+        <v>-0.2723</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.0196</v>
+        <v>-2.2971</v>
       </c>
       <c r="J21" t="n">
-        <v>0.2242</v>
+        <v>-1.4529</v>
       </c>
       <c r="K21" t="n">
-        <v>0.1815</v>
+        <v>-0.6197</v>
       </c>
       <c r="L21" t="n">
-        <v>0.0427</v>
+        <v>-0.8332000000000001</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.723</v>
+        <v>-1.1165</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6607</v>
+        <v>0.3474</v>
       </c>
       <c r="O21" t="n">
-        <v>-1.0623</v>
+        <v>-1.4639</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.3887</v>
+        <v>0.3968</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.9838</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>0.5952</v>
+        <v>0.3968</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.3622</v>
+        <v>-0.1941</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1133</v>
+        <v>-0.238</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2489</v>
+        <v>0.0439</v>
       </c>
       <c r="V21" t="n">
-        <v>-1.2065</v>
+        <v>-1.8097</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>-0.3373</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.2065</v>
+        <v>-1.4724</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. DUCH CABEZAS</t>
+          <t>V. VINÓS ALTEMIR</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-4.9068</v>
+        <v>-4.2343</v>
       </c>
       <c r="E22" t="n">
-        <v>-2.5383</v>
+        <v>-1.5669</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.3685</v>
+        <v>-2.6673</v>
       </c>
       <c r="G22" t="n">
-        <v>-2.5694</v>
+        <v>-1.4988</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2723</v>
+        <v>-0.4792</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.2971</v>
+        <v>-1.0196</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.4529</v>
+        <v>0.2242</v>
       </c>
       <c r="K22" t="n">
-        <v>-0.6197</v>
+        <v>0.1815</v>
       </c>
       <c r="L22" t="n">
-        <v>-0.8332000000000001</v>
+        <v>0.0427</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1165</v>
+        <v>-1.723</v>
       </c>
       <c r="N22" t="n">
-        <v>0.3474</v>
+        <v>-0.6607</v>
       </c>
       <c r="O22" t="n">
-        <v>-1.4639</v>
+        <v>-1.0623</v>
       </c>
       <c r="P22" t="n">
-        <v>0.3968</v>
+        <v>-1.3887</v>
       </c>
       <c r="Q22" t="n">
+        <v>-1.9838</v>
+      </c>
+      <c r="R22" t="n">
+        <v>0.5952</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1403</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0.1927</v>
+      </c>
+      <c r="U22" t="n">
+        <v>-0.3331</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.2065</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
-        <v>0.3968</v>
-      </c>
-      <c r="S22" t="n">
-        <v>-0.9245</v>
-      </c>
-      <c r="T22" t="n">
-        <v>-0.7481</v>
-      </c>
-      <c r="U22" t="n">
-        <v>-0.1763</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-1.8097</v>
-      </c>
-      <c r="W22" t="n">
-        <v>-0.3373</v>
-      </c>
       <c r="X22" t="n">
-        <v>-1.4724</v>
+        <v>-1.2065</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2361</v>
+        <v>-4.2516</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.9177</v>
+        <v>-4.1015</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.3184</v>
+        <v>-0.1501</v>
       </c>
       <c r="G23" t="n">
         <v>-4.2893</v>
@@ -2248,13 +2248,13 @@
         <v>1.5871</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.3275</v>
+        <v>-0.3429</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.9975000000000001</v>
+        <v>-0.1813</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.3299</v>
+        <v>-0.1616</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2065</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-13.6251</v>
+        <v>-12.9451</v>
       </c>
       <c r="E24" t="n">
-        <v>2.9983</v>
+        <v>2.9984</v>
       </c>
       <c r="F24" t="n">
-        <v>-16.6234</v>
+        <v>-15.9432</v>
       </c>
       <c r="G24" t="n">
         <v>-4.672000000000001</v>
@@ -2326,13 +2326,13 @@
         <v>14.8789</v>
       </c>
       <c r="S24" t="n">
-        <v>-2.0405</v>
+        <v>-1.3603</v>
       </c>
       <c r="T24" t="n">
-        <v>2.7784</v>
+        <v>2.7783</v>
       </c>
       <c r="U24" t="n">
-        <v>-4.818700000000001</v>
+        <v>-4.1387</v>
       </c>
       <c r="V24" t="n">
         <v>-2.945</v>
